--- a/raw_data/about.xlsx
+++ b/raw_data/about.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作经历" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学术兼职与职称" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教育经历" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="荣誉奖项" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="期刊文章" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会议文章" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="美国专利" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中国专利" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="工作经历" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="学术兼职与职称" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="教育经历" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="荣誉奖项" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="期刊文章" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="会议文章" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="美国专利" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="中国专利" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -545,7 +545,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  教育经历：序号|开始|结束|学校中|学校英|国家|学位|专业|导师|备注</t>
+          <t xml:space="preserve">  教育经历：序号|开始|结束|学校中|学校英|国家|学位|专业|导师|备注|国家(英)|学位(英)|专业(英)</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1515,6 +1515,21 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>国家(英)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>学位(英)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>专业(英)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="6" t="n">
@@ -1561,6 +1576,21 @@
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Spatial Audio Signal Processing</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6" t="n">
@@ -1607,6 +1637,21 @@
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Bachelor of Engineering</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Telecommunications Engineering and Management (Joint Program)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="6" t="n">
@@ -1653,6 +1698,21 @@
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Bachelor of Engineering</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Telecommunications Engineering and Management (Joint Program)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
